--- a/02_Data/segment/02_3_Profile_Kmeans_clustering_with_silhouette_labeled_ppt용.xlsx
+++ b/02_Data/segment/02_3_Profile_Kmeans_clustering_with_silhouette_labeled_ppt용.xlsx
@@ -8,79 +8,117 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project2\Chill_Tuna\02_Data\segment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D1304FE-BE9C-465A-8593-2604F9312E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{53242DE3-2774-4D64-B712-C3A6C30416C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3132" yWindow="2076" windowWidth="15480" windowHeight="9888" xr2:uid="{37BFFBFB-A521-428E-8D2D-793E860CEFE7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{37BFFBFB-A521-428E-8D2D-793E860CEFE7}"/>
   </bookViews>
   <sheets>
     <sheet name="02_3_Profile_Kmeans_clustering_" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
   <si>
     <t>cluster</t>
   </si>
   <si>
-    <t>'brand_loyalty'_scaled</t>
-  </si>
-  <si>
-    <t>'cooking_convenience'_scaled</t>
-  </si>
-  <si>
-    <t>'health_orientation'_scaled</t>
-  </si>
-  <si>
-    <t>'hmr_preference'_scaled</t>
-  </si>
-  <si>
-    <t>'premium_orientation'_scaled</t>
-  </si>
-  <si>
-    <t>'price_sensitivity'_scaled</t>
-  </si>
-  <si>
-    <t>'variety_seeking'_scaled</t>
-  </si>
-  <si>
     <t>label</t>
   </si>
   <si>
     <t>description</t>
   </si>
   <si>
+    <t>가격이나 브랜드에 크게 구애받지 않고 건강을 최우선으로 고려하는 프리미엄 소비자 그룹입니다. 건강과 편리성을 모두 만족시키는 제품에 기꺼이 지갑을 엽니다.</t>
+  </si>
+  <si>
+    <t>식품 구매 자체에 관심이 적고, HMR이나 가공식품의 편리함에도 크게 동요하지 않는 그룹입니다. 가격에 매우 민감하며, 필수적인 경우에만 구매하는 경향이 있습니다.</t>
+  </si>
+  <si>
+    <t>자신의 취향과 경험을 중시하는 소비자 그룹입니다. 단순히 배를 채우는 것 이상의 가치를 추구하며, 새로운 제품을 가장 먼저 경험하고 공유하려는 경향이 강합니다</t>
+  </si>
+  <si>
+    <t>brand_loyalty_scaled</t>
+  </si>
+  <si>
+    <t>cooking_convenience_scaled</t>
+  </si>
+  <si>
+    <t>health_orientation_scaled</t>
+  </si>
+  <si>
+    <t>hmr_preference_scaled</t>
+  </si>
+  <si>
+    <t>premium_orientation_scaled</t>
+  </si>
+  <si>
+    <t>price_sensitivity_scaled</t>
+  </si>
+  <si>
+    <t>variety_seeking_scaled</t>
+  </si>
+  <si>
+    <t>brand_loyalty
+_scaled</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>cooking_convenience_scaled</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>health_orientation_scaled</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>hmr_preference
+_scaled</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>premium_orientation_scaled</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>price_sensitivity
+_scaled</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>variety_seeking
+_scaled</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>실속형 미식가</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>편리성을 중시하면서도 새로운 맛과 제품을 시도하는 데 적극적인 소비자 그룹입니다. 가격에 민감하기보다는 효율성과 맛을 동시에 추구합니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>건강 추구형 소비자</t>
-  </si>
-  <si>
-    <t>가격이나 브랜드에 크게 구애받지 않고 건강을 최우선으로 고려하는 프리미엄 소비자 그룹입니다. 건강과 편리성을 모두 만족시키는 제품에 기꺼이 지갑을 엽니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>구매 소극적 소비자</t>
-  </si>
-  <si>
-    <t>식품 구매 자체에 관심이 적고, HMR이나 가공식품의 편리함에도 크게 동요하지 않는 그룹입니다. 가격에 매우 민감하며, 필수적인 경우에만 구매하는 경향이 있습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>트렌드 주도형 소비자</t>
-  </si>
-  <si>
-    <t>자신의 취향과 경험을 중시하는 소비자 그룹입니다. 단순히 배를 채우는 것 이상의 가치를 추구하며, 새로운 제품을 가장 먼저 경험하고 공유하려는 경향이 강합니다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -240,8 +278,17 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -421,8 +468,26 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -537,6 +602,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -666,9 +746,24 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1033,31 +1128,31 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="J1" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.4">
@@ -1086,10 +1181,10 @@
         <v>0.483350993377483</v>
       </c>
       <c r="I2" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.4">
@@ -1118,10 +1213,10 @@
         <v>0.247929915639195</v>
       </c>
       <c r="I3" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="J3" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.4">
@@ -1150,10 +1245,10 @@
         <v>0.28084239130434702</v>
       </c>
       <c r="I4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J4" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.4">
@@ -1182,10 +1277,154 @@
         <v>0.54399023725734996</v>
       </c>
       <c r="I5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F88E3A-05CE-4179-BC74-AEA4FF9D0EC6}">
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="8" width="16.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J5" t="s">
+      <c r="F1" s="3" t="s">
         <v>17</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0.31846891370959701</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0.54501793131596599</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.30882448525641398</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0.79457485519325899</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0.26401233902107502</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0.36469538952396402</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0.483350993377483</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0.37744610281923702</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0.44520850588595201</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.65665990295704302</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0.808208386731052</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0.49624407819750299</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0.31539514046106298</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0.247929915639195</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5">
+        <v>0.218983208955223</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0.10165351371664701</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0.33178844056706602</v>
+      </c>
+      <c r="E4" s="5">
+        <v>1.22428991185111E-2</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0.23681799674267101</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0.260456438736549</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0.28084239130434702</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.63024433965940496</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.54828717290560902</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0.374844466716589</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0.84052776804596896</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.44848614997321001</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0.35708608575315098</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.54399023725734996</v>
       </c>
     </row>
   </sheetData>
